--- a/PTBR/Lang/PTBR/Game/Religion.xlsx
+++ b/PTBR/Lang/PTBR/Game/Religion.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eyth do Vazio  </t>
+          <t>Eyth do Vazio</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outrora um dos Deuses mais renomados, ele caiu no Vazio após as maquinações de Mani e Lulwy o levarem a romper um pacto ancestral.  </t>
+          <t>Um dos deuses mais renomados, caiu no Vazio depois que a maquinação de Mani e Lulwy o levou a quebrar um pacto antigo.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eyth não concede bênçãos.  </t>
+          <t>Eyth não concede bênçãos.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vazio  </t>
+          <t>Vazio</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lulwy do Vento  </t>
+          <t>Lulwy do Vento</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">A deusa dos ventos e de espírito livre, Lulwy valoriza a liberdade acima de tudo e ninguém pode restringi-la. No entanto, devido ao seu gosto sádico, ela prefere dominar os outros física e mentalmente. Seu deslumbrante corpo nu atrai muitos devotos.  </t>
+          <t>A deusa ventosa e de espírito livre valoriza a liberdade acima de tudo e ninguém pode prendê-la. Contudo, por gosto sádico, prefere dominar os outros no corpo e na mente. Seu corpo nu deslumbrante atrai muitos devotos.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os fiéis de Lulwy recebem a bênção do vento e podem se mover rapidamente.  </t>
+          <t>Os fiéis de Lulwy recebem a bênção do vento e podem se mover velozmente.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deusa  </t>
+          <t>Deusa</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opatos da Terra  </t>
+          <t>Opatos da Terra</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Um dos Deuses primordiais, o Deus da Terra, carrega muitos mistérios e trevas ocultas por trás de seus olhos de ferro avermelhado. Metade de seu corpo é coberta por uma pedra cristalina de outro mundo, e suas asas são endurecidas. Geralmente é calmo, mas possui um lado beligerante e feroz. Ele é um guerreiro feroz e violento do mundo divino, que às vezes parece estar em um sono profundo como uma rocha, mas de repente rompe as proibições dos deuses e interfere na terra. Em suas guerras contra os Deuses Corrompidos, deixou um rastro de cadáveres, tanto de amigos quanto de inimigos, sendo altamente respeitado pelos guerreiros.  </t>
+          <t>Um dos deuses primordiais, o Deus da Terra, guarda muitos mistérios e trevas por trás de seus olhos de ferro vermelho. Metade do corpo é coberta por uma pedra cristalina de outro mundo, e as asas são endurecidas. Costuma ser manso, mas tem um lado belicoso e feroz. É um guerreiro violento e impiedoso do mundo divino que às vezes parece dormir profundamente como uma rocha, mas de repente quebra as proibições dos deuses e interfere na terra. Em suas guerras contra os Deuses Corrompidos, dizimou muitos cadáveres, de amigos e inimigos igualmente, e é altamente respeitado pelos guerreiros.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os fiéis de Opatos possuem imensa força e defesa.  </t>
+          <t>Os fiéis de Opatos têm força e defesa colossais.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deus  </t>
+          <t>Deus</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Itzpalt do Elemento  </t>
+          <t>Itzpalt do Elemento</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O duque de cabelos vermelhos que existe desde os tempos mais antigos e se orgulha de ser o chefe dos Deuses. Suas asas, que brilham em cinco cores, às vezes são envoltas por chamas que consomem tudo, e outras vezes por um orvalho que congela tudo. Houve um tempo em que caiu em desespero por não ter conseguido evitar a morte de sua amada Deusa Odina, mas recentemente tem se recuperado.  </t>
+          <t>O duque ruivo que existe desde os tempos mais antigos e se orgulha de ser o chefe dos Deuses. Suas asas, que trocam o brilho em cinco cores, às vezes se cobrem de uma chama que consome tudo, às vezes de um orvalho que congela tudo. Houve um tempo em que mergulhou no desespero pelo remorso de não ter evitado a morte de sua amada deusa Odina, mas recentemente vem se recuperando.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os fiéis de Itzpalt são protegidos contra danos elementais e aprendem a absorver mana do ambiente.  </t>
+          <t>Os fiéis de Itzpalt são protegidos dos danos elementais e aprendem a absorver mana do ambiente.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deus  </t>
+          <t>Deus</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mani da Máquina  </t>
+          <t>Mani da Máquina</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ele é um herege de coração frio, meio humano e meio máquina, que, através de enganos e intrigas, usurpou o trono do Deus antigo. Seu poder ainda é incalculável. Para ele, a existência dos deuses e sua providência são ilógicas, e seu objetivo imediato é o extermínio dos deuses, visando, no fim, estabelecer uma sociedade governada inteiramente por máquinas.  </t>
+          <t>É um herege de coração frio, metade humano e metade máquina, que por trapaça e intriga usurpou o trono do Deus antigo. Seu poder ainda é incomensurável. Para ele, a existência dos deuses e sua providência são ilógicas, e seu objetivo imediato é matar deuses, mirando por fim numa sociedade inteiramente governada por máquinas.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os fiéis de Mani adquirem vasto conhecimento sobre máquinas e aprendem a usá-las de forma eficaz.  </t>
+          <t>Os fiéis de Mani recebem imenso conhecimento de máquinas e aprendem a usá-las com eficiência.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deus  </t>
+          <t>Deus</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kumiromi da Colheita  </t>
+          <t>Kumiromi da Colheita</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ele e seu irmão vagaram pelo universo como esporos e enraizaram-se na terra de Ylva nos tempos antigos. Ama e protege todas as formas de vida que nascem e crescem, sem distinção. Não se envolve em disputas de facções no mundo divino e frequentemente age como intermediário entre os outros Deuses e Deusas.  </t>
+          <t>Ele e seu irmão vagaram pelo universo como esporos e criaram raiz na terra de Ylva nos tempos antigos. Ama e vigia toda a vida que nasce e cresce, sem distinção. Não se mete nas disputas de facções do mundo divino e muitas vezes age como intermediário entre os outros Deuses e Deusas.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os fiéis de Kumiromi recebem as bênçãos da natureza.  </t>
+          <t>Os fiéis de Kumiromi recebem as bênçãos da natureza.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deus  </t>
+          <t>Deus</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ehekatl da Sorte  </t>
+          <t>Ehekatl da Sorte</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Deusa Ehekatl nasceu como a sétima filha do rei dos Deuses Gatos, sendo considerada portadora de boa fortuna. Superando muitos desastres causados por sua irmã, ascendeu à posição de Deusa com a ajuda de Kumiromi. Por oferecer benefícios a todos, tem muitos seguidores de todas as idades e gêneros. Recentemente, devido a um certo incidente, sua mentalidade tem regredido para a de um gato.  </t>
+          <t>A deusa Ehekatl nasceu do rei do Deus-Gato como sua sétima filha, a que diziam trazer boa sorte. Superando muitos desastres trazidos pela irmã, foi elevada a deusa com a ajuda de Kumiromi. Por seus benefícios para todas as ocasiões, tem muitos seguidores, jovens e velhos, homens e mulheres. No momento, sua mente está regredindo à de gato por causa de um certo incidente.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os fiéis de Ehekatl são extremamente sortudos.  </t>
+          <t>Os fiéis de Ehekatl são realmente sortudos.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deusa  </t>
+          <t>Deusa</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jure da Cura  </t>
+          <t>Jure da Cura</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ela é uma graciosa Deusa da inocência, com belos olhos cor de jade e uma linhagem de divindades ancestrais. É a irmã mais nova das deusas Odina e Eris, mas sua memória sobre Eris é falha, e os outros Deuses se recusam a falar sobre o assunto. Acredita-se que as penas que caem de suas pequenas asas na cabeça podem curar todas as doenças, e penas falsas são vendidas a preços altos na terra. Ela é sincera, gentil, mas às vezes excessivamente zelosa. Por alguma razão, tem muitos seguidores radicais.  </t>
+          <t>É uma graciosa deusa da inocência, de belos olhos verde-jade e linhagem de deidades antigas. É a irmã mais nova das deusas Odina e Eris, mas suas memórias de Eris estão falhas e os outros Deuses se recusam a tocar no assunto. Dizem que as penas que caem das pequenas asas de sua cabeça curam toda doença, e penas falsas são vendidas por alto preço na terra. É sincera, gentil, mas às vezes implicante. Por algum motivo, tem muitos seguidores radicais.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os fiéis de Jure podem curar ferimentos.  </t>
+          <t>Os fiéis de Jure podem curar feridas.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deusa  </t>
+          <t>Deusa</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yakasha do Esquecimento  </t>
+          <t>Yakasha do Olvido</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nascida como a quarta filha de Elin, a Viúva Branca, foi capturada pela Bruxa de Ravenwood ainda criança, e até a memória de sua existência foi apagada de sua mãe. Aprisionada em um quarto escuro na Torre Enevoada, cresceu sem conhecimento do mundo exterior, sendo criada como uma ferramenta de vingança pela bruxa que odiava Elin. Mesmo ao matar as filhas de Elin, jamais percebeu que eram suas irmãs. Eventualmente, seu despertar trouxe desordem a Ylva.  </t>
+          <t>Nascida como a quarta filha de Elin, a Viúva Branca, foi capturada pela Bruxa de Ravenwood quando criança, e até a memória de sua existência foi apagada da mãe. Presa num quarto escuro da Torre Nevoeira, cresceu sem conhecer o mundo exterior como ferramenta de vingança da bruxa que odiava Elin. Mesmo depois de matar filhas de Elin, nunca soube que eram suas irmãs. Por fim, o despertar da garota fez Ylva começar a se desfazer.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desconhecido  </t>
+          <t>Desconhecido</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deusa  </t>
+          <t>Deusa</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Obliteração,Yakasha</t>
+          <t>Olvido,Yakasha</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elin da Harmonia  </t>
+          <t>Elin da Harmonia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elin, a filha há muito perdida de Odina, foi criada na terra a pedido de Itzpalt, que desejava mantê-la afastada do caos e dos conflitos do mundo divino. Sua presença trouxe harmonia e prosperidade ao mundo, e os humanos a adoravam. Ela é uma garota íntegra, com um forte senso de justiça e respeito pela ordem, mas, possuindo uma aparência nobre e delicada que atrai fortemente alguns homens, também tem um lado sedutor do qual não tem consciência. É profundamente odiada pela Bruxa de Ravenwood, pois, sem querer, roubou o marido da bruxa.  </t>
+          <t>Elin, a filha perdida de Odina, foi criada na terra a pedido de Itzpalt, que queria mantê-la longe do caos e das disputas do mundo divino. Sua presença trouxe harmonia e prosperidade ao mundo, e os humanos a adoravam. É uma garota íntegra, de forte senso de justiça e respeito pela ordem, mas com uma aparência nobre e delicada que atrai fortemente alguns homens, e também tem um lado demoníaco de que ela própria não sabe. É profundamente odiada pela Bruxa de Ravenwood porque, sem querer, roubou o marido da bruxa.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desconhecido  </t>
+          <t>Desconhecido</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deusa  </t>
+          <t>Deusa</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kizuami da Trapaça  </t>
+          <t>Kizuami da Trapaça</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">O caprichoso e brincalhão guardião de Mifu, conhecido por conceder bênçãos e maldições, é amplamente reverenciado entre as tribos de raposas como o irmão mais velho atencioso da Deusa da Sombra Lunar, Horome. Sempre em busca de novas e interessantes experiências, é fascinado pela imprevisibilidade dos humanos e gosta de interagir com o mundo mortal tanto quanto as regras divinas permitem. Sua natureza fraternal e cuidadosa, combinada com um desdém travesso pela seriedade, é amplamente reconhecida.  </t>
+          <t>O guardião caprichoso e brincalhão dos Mifu, conhecido por supervisionar bênçãos e maldições, também é amplamente cultuado entre as tribos de raposas como o irmão mais velho cuidadoso da deusa Horome da Sombralua. Sempre atrás de experiências novas e interessantes, é fascinado pela imprevisibilidade dos humanos e gosta de interagir com o reino mortal tanto quanto as regras divinas permitem. Sua natureza fraterna e cuidadosa, unida a um desprezo tipicamente raposo pela seriedade, é bem conhecida.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os fiéis de Kizuami aprendem a arte de maximizar bênçãos e maldições.  </t>
+          <t>Os fiéis de Kizuami aprendem a arte de maximizar bênçãos e maldições.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deus  </t>
+          <t>Deus</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horome da Sombra da Lua  </t>
+          <t>Horome da Sombralua</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Deusa de Nefu, que adora canto e dança. Recebe apoio generalizado entre as espécies por sua presença maternal e efêmera. Nos tempos antigos, uniu forças com seu querido irmão Kizuami, empunhando um par de lâminas sagradas para separar corpo e alma de Yufu, um traidor que se aliou aos Deuses da Negentropia. Sua silhueta, dançando com espadas sob a luz da lua, é uma visão de beleza trágica que inspirou inúmeras peças teatrais.  </t>
+          <t>A deusa dos Nefu, que adora canto e dança. Recebe amplo apoio entre as espécies por seu rosto maternal e ao mesmo tempo efêmero. Nos tempos antigos, uniu-se ao amado irmão Kizuami e, com um par de lâminas sagradas, cortou o corpo e a alma de Yufu, uma traidora que se aliou aos Deuses da Negaentropia. Sua silhueta, dançando com espadas sob o luar, é uma visão de beleza trágica que inspirou incontáveis peças.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os fiéis de Horome dominam as artes da magia e da esgrima.  </t>
+          <t>Os fiéis de Horome dominam as artes da magia e da espada.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deusa  </t>
+          <t>Deusa</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sombra da Lua,Horome</t>
+          <t>Sombralua,Horome</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eavan, a Catástrofe da Guerra.</t>
+          <t>Yevan da Discórdia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yevan, o deus que governa a guerra, é conhecido como uma anomalia entre as divindades por sua falta de interesse nas disputas divinas e seu foco em interagir com o mundo mortal. Enxergando o conflito como a força motriz por trás da evolução e da harmonia da vida, ele considera os intermináveis combates e devastações da guerra entre os humanos como algo supremamente deleitável. Frequentemente visto trajando vestes simples no pós-batalha, sua postura educada oculta declarações ameaçadoras, tornando-o tão perigoso quanto Opatos entre os deuses.  </t>
+          <t>Yevan, o deus que preside a guerra, é uma figura esquisita entre as deidades: não se interessa por brigas divinas e foca em interagir com o mundo mortal. Vendo o conflito como o motor da evolução e da harmonia da vida, acha as lutas infinitas e os estragos da guerra entre humanos absolutamente deliciosos. Visto com frequência em mantos simples após as batalhas, seu jeito educado esconde a predileção por declarações sinistras, e entre os deuses ele é considerado tão perigoso quanto Opartos.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Os fiéis de Yevan recebem o poder da destruição para superar os desafios da batalha.  </t>
+          <t>Os fiéis de Yevan recebem o poder da destruição para superar as provas da batalha.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deus  </t>
+          <t>Deus</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Conflito,Yevan</t>
+          <t>Discórdia,Yevan</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
